--- a/datoslimpios/deudapublica-limpio.xlsx
+++ b/datoslimpios/deudapublica-limpio.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:F193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,16 @@
           <t>Deuda Per Cápita</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -465,6 +475,12 @@
       <c r="D2" t="n">
         <v>38712</v>
       </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">España </t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,6 +497,12 @@
       <c r="D3" t="n">
         <v>35570</v>
       </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alemania </t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -497,6 +519,12 @@
       <c r="D4" t="n">
         <v>54045</v>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reino Unido </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -513,6 +541,12 @@
       <c r="D5" t="n">
         <v>52108</v>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Francia </t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -529,6 +563,12 @@
       <c r="D6" t="n">
         <v>54459</v>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italia </t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -545,6 +585,12 @@
       <c r="D7" t="n">
         <v>27251</v>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Portugal </t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -561,6 +607,12 @@
       <c r="D8" t="n">
         <v>105374</v>
       </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estados Unidos </t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -577,6 +629,12 @@
       <c r="D9" t="n">
         <v>81219</v>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japón </t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -593,6 +651,12 @@
       <c r="D10" t="n">
         <v>11759</v>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">China </t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -609,6 +673,12 @@
       <c r="D11" t="n">
         <v>15782</v>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Andorra </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,6 +695,12 @@
       <c r="D12" t="n">
         <v>15616</v>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emiratos Árabes Unidos </t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -641,6 +717,12 @@
       <c r="D13" t="n">
         <v>34</v>
       </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Afganistán </t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -657,6 +739,12 @@
       <c r="D14" t="n">
         <v>14627</v>
       </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antigua y Barbuda </t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -673,6 +761,12 @@
       <c r="D15" t="n">
         <v>6421</v>
       </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Albania </t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -689,6 +783,12 @@
       <c r="D16" t="n">
         <v>4215</v>
       </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armenia </t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -705,6 +805,12 @@
       <c r="D17" t="n">
         <v>1878</v>
       </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Angola </t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -721,6 +827,12 @@
       <c r="D18" t="n">
         <v>11846</v>
       </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argentina </t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -737,6 +849,12 @@
       <c r="D19" t="n">
         <v>46025</v>
       </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Austria </t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -753,6 +871,12 @@
       <c r="D20" t="n">
         <v>33233</v>
       </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Australia </t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -769,6 +893,12 @@
       <c r="D21" t="n">
         <v>1575</v>
       </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Azerbaiyán </t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -785,6 +915,12 @@
       <c r="D22" t="n">
         <v>2567</v>
       </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bosnia y Herzegovina </t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -801,6 +937,12 @@
       <c r="D23" t="n">
         <v>26500</v>
       </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Barbados </t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -817,6 +959,12 @@
       <c r="D24" t="n">
         <v>1052</v>
       </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bangladés </t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -833,6 +981,12 @@
       <c r="D25" t="n">
         <v>58537</v>
       </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bélgica </t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -849,6 +1003,12 @@
       <c r="D26" t="n">
         <v>575</v>
       </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Burkina Faso </t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -865,6 +1025,12 @@
       <c r="D27" t="n">
         <v>4198</v>
       </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bulgaria </t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -881,6 +1047,12 @@
       <c r="D28" t="n">
         <v>36035</v>
       </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baréin </t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -897,6 +1069,12 @@
       <c r="D29" t="n">
         <v>179</v>
       </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Burundi </t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -913,6 +1091,12 @@
       <c r="D30" t="n">
         <v>814</v>
       </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Benin </t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -929,6 +1113,12 @@
       <c r="D31" t="n">
         <v>781</v>
       </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brunéi </t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -945,6 +1135,12 @@
       <c r="D32" t="n">
         <v>3743</v>
       </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bolivia </t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -961,6 +1157,12 @@
       <c r="D33" t="n">
         <v>8986</v>
       </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brasil </t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -977,6 +1179,12 @@
       <c r="D34" t="n">
         <v>28748</v>
       </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bahamas </t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -993,6 +1201,12 @@
       <c r="D35" t="n">
         <v>4245</v>
       </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bután </t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1009,6 +1223,12 @@
       <c r="D36" t="n">
         <v>1759</v>
       </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Botsuana </t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1025,6 +1245,12 @@
       <c r="D37" t="n">
         <v>3328</v>
       </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bielorrusia </t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1041,6 +1267,12 @@
       <c r="D38" t="n">
         <v>5102</v>
       </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Belice </t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1057,6 +1289,12 @@
       <c r="D39" t="n">
         <v>60521</v>
       </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canadá </t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1073,6 +1311,12 @@
       <c r="D40" t="n">
         <v>182</v>
       </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">República Democrática del Congo </t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1089,6 +1333,12 @@
       <c r="D41" t="n">
         <v>322</v>
       </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">República Centroafricana </t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1105,6 +1355,12 @@
       <c r="D42" t="n">
         <v>2296</v>
       </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">República del Congo </t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1121,6 +1377,12 @@
       <c r="D43" t="n">
         <v>38891</v>
       </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suiza </t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1137,6 +1399,12 @@
       <c r="D44" t="n">
         <v>1656</v>
       </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costa de Marfil </t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1153,6 +1421,12 @@
       <c r="D45" t="n">
         <v>6996</v>
       </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chile </t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1169,6 +1443,12 @@
       <c r="D46" t="n">
         <v>800</v>
       </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Camerún </t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1185,6 +1465,12 @@
       <c r="D47" t="n">
         <v>4867</v>
       </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colombia </t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1201,6 +1487,12 @@
       <c r="D48" t="n">
         <v>10701</v>
       </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costa Rica </t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1217,6 +1509,12 @@
       <c r="D49" t="n">
         <v>5922</v>
       </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cabo Verde </t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1233,6 +1531,12 @@
       <c r="D50" t="n">
         <v>24050</v>
       </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chipre </t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1249,6 +1553,12 @@
       <c r="D51" t="n">
         <v>13787</v>
       </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chequia </t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1265,6 +1575,12 @@
       <c r="D52" t="n">
         <v>1352</v>
       </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yibuti </t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1281,6 +1597,12 @@
       <c r="D53" t="n">
         <v>22281</v>
       </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dinamarca </t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1297,6 +1619,12 @@
       <c r="D54" t="n">
         <v>10145</v>
       </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dominica </t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1313,6 +1641,12 @@
       <c r="D55" t="n">
         <v>6785</v>
       </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">República Dominicana </t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1329,6 +1663,12 @@
       <c r="D56" t="n">
         <v>2814</v>
       </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Argelia </t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1345,6 +1685,12 @@
       <c r="D57" t="n">
         <v>3727</v>
       </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ecuador </t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1361,6 +1707,12 @@
       <c r="D58" t="n">
         <v>7367</v>
       </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estonia </t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1377,6 +1729,12 @@
       <c r="D59" t="n">
         <v>3311</v>
       </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Egipto </t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1393,6 +1751,12 @@
       <c r="D60" t="n">
         <v>1153</v>
       </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eritrea </t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1409,6 +1773,12 @@
       <c r="D61" t="n">
         <v>481</v>
       </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Etiopía </t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1425,6 +1795,12 @@
       <c r="D62" t="n">
         <v>43525</v>
       </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finlandia </t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1441,6 +1817,12 @@
       <c r="D63" t="n">
         <v>4953</v>
       </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fiyi </t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1457,6 +1839,12 @@
       <c r="D64" t="n">
         <v>688</v>
       </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estados Federados de Micronesia </t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1473,6 +1861,12 @@
       <c r="D65" t="n">
         <v>5698</v>
       </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gabón </t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1489,6 +1883,12 @@
       <c r="D66" t="n">
         <v>8512</v>
       </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granada </t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1505,6 +1905,12 @@
       <c r="D67" t="n">
         <v>3291</v>
       </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Georgia </t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1521,6 +1927,12 @@
       <c r="D68" t="n">
         <v>1885</v>
       </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghana </t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1537,6 +1949,12 @@
       <c r="D69" t="n">
         <v>681</v>
       </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gambia </t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1553,6 +1971,12 @@
       <c r="D70" t="n">
         <v>821</v>
       </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guinea </t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1569,6 +1993,12 @@
       <c r="D71" t="n">
         <v>2610</v>
       </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guinea Ecuatorial </t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1585,6 +2015,12 @@
       <c r="D72" t="n">
         <v>38364</v>
       </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grecia </t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1601,6 +2037,12 @@
       <c r="D73" t="n">
         <v>1644</v>
       </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guatemala </t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1617,6 +2059,12 @@
       <c r="D74" t="n">
         <v>835</v>
       </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guinea-Bisáu </t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1633,6 +2081,12 @@
       <c r="D75" t="n">
         <v>5456</v>
       </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guyana </t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1649,6 +2103,12 @@
       <c r="D76" t="n">
         <v>5133</v>
       </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hong Kong </t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1665,6 +2125,12 @@
       <c r="D77" t="n">
         <v>1638</v>
       </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Honduras </t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1681,6 +2147,12 @@
       <c r="D78" t="n">
         <v>13764</v>
       </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Croacia </t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1697,6 +2169,12 @@
       <c r="D79" t="n">
         <v>337</v>
       </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haití </t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1713,6 +2191,12 @@
       <c r="D80" t="n">
         <v>17175</v>
       </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hungría </t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1729,6 +2213,12 @@
       <c r="D81" t="n">
         <v>1992</v>
       </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indonesia </t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1745,6 +2235,12 @@
       <c r="D82" t="n">
         <v>43395</v>
       </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Irlanda </t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1761,6 +2257,12 @@
       <c r="D83" t="n">
         <v>36724</v>
       </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Israel </t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1777,6 +2279,12 @@
       <c r="D84" t="n">
         <v>2055</v>
       </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">India </t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1793,6 +2301,12 @@
       <c r="D85" t="n">
         <v>2873</v>
       </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Irak </t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1809,6 +2323,12 @@
       <c r="D86" t="n">
         <v>1636</v>
       </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Irán </t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1825,6 +2345,12 @@
       <c r="D87" t="n">
         <v>50833</v>
       </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Islandia </t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1841,6 +2367,12 @@
       <c r="D88" t="n">
         <v>4941</v>
       </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jamaica </t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1857,6 +2389,12 @@
       <c r="D89" t="n">
         <v>4252</v>
       </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jordania </t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1873,6 +2411,12 @@
       <c r="D90" t="n">
         <v>1452</v>
       </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kenia </t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1889,6 +2433,12 @@
       <c r="D91" t="n">
         <v>924</v>
       </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kirguistán </t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1905,6 +2455,12 @@
       <c r="D92" t="n">
         <v>702</v>
       </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Camboya </t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1921,6 +2477,12 @@
       <c r="D93" t="n">
         <v>266</v>
       </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kiribati </t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1937,6 +2499,12 @@
       <c r="D94" t="n">
         <v>545</v>
       </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comoras </t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1953,6 +2521,12 @@
       <c r="D95" t="n">
         <v>12425</v>
       </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Cristóbal y Nieves </t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1969,6 +2543,12 @@
       <c r="D96" t="n">
         <v>18052</v>
       </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corea del Sur </t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1985,6 +2565,12 @@
       <c r="D97" t="n">
         <v>1055</v>
       </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kuwait </t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2001,6 +2587,12 @@
       <c r="D98" t="n">
         <v>3024</v>
       </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kazajistán </t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2017,6 +2609,12 @@
       <c r="D99" t="n">
         <v>2085</v>
       </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laos </t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2033,6 +2631,12 @@
       <c r="D100" t="n">
         <v>12669</v>
       </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Líbano </t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2049,6 +2653,12 @@
       <c r="D101" t="n">
         <v>10260</v>
       </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santa Lucía </t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2065,6 +2675,12 @@
       <c r="D102" t="n">
         <v>973</v>
       </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liechtenstein </t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2081,6 +2697,12 @@
       <c r="D103" t="n">
         <v>4529</v>
       </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sri Lanka </t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2097,6 +2719,12 @@
       <c r="D104" t="n">
         <v>487</v>
       </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liberia </t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2113,6 +2741,12 @@
       <c r="D105" t="n">
         <v>584</v>
       </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesoto </t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2129,6 +2763,12 @@
       <c r="D106" t="n">
         <v>11219</v>
       </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lituania </t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2145,6 +2785,12 @@
       <c r="D107" t="n">
         <v>35946</v>
       </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luxemburgo </t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2161,6 +2807,12 @@
       <c r="D108" t="n">
         <v>10955</v>
       </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Letonia </t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2177,6 +2829,12 @@
       <c r="D109" t="n">
         <v>2583</v>
       </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libia </t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2193,6 +2851,12 @@
       <c r="D110" t="n">
         <v>2911</v>
       </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marruecos </t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2209,6 +2873,12 @@
       <c r="D111" t="n">
         <v>2964</v>
       </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moldavia </t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2225,6 +2895,12 @@
       <c r="D112" t="n">
         <v>8063</v>
       </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Montenegro </t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2241,6 +2917,12 @@
       <c r="D113" t="n">
         <v>281</v>
       </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Madagascar </t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2257,6 +2939,12 @@
       <c r="D114" t="n">
         <v>1200</v>
       </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Islas Marshall </t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2273,6 +2961,12 @@
       <c r="D115" t="n">
         <v>5018</v>
       </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Macedonia del Norte </t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2289,6 +2983,12 @@
       <c r="D116" t="n">
         <v>462</v>
       </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Malí </t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2305,6 +3005,12 @@
       <c r="D117" t="n">
         <v>595</v>
       </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Myanmar </t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2321,6 +3027,12 @@
       <c r="D118" t="n">
         <v>2957</v>
       </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mongolia </t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2337,6 +3049,12 @@
       <c r="D119" t="n">
         <v>1006</v>
       </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mauritania </t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2353,6 +3071,12 @@
       <c r="D120" t="n">
         <v>20073</v>
       </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Malta </t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2369,6 +3093,12 @@
       <c r="D121" t="n">
         <v>9570</v>
       </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mauricio </t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2385,6 +3115,12 @@
       <c r="D122" t="n">
         <v>17874</v>
       </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maldivas </t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2401,6 +3137,12 @@
       <c r="D123" t="n">
         <v>455</v>
       </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Malaui </t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2417,6 +3159,12 @@
       <c r="D124" t="n">
         <v>8183</v>
       </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">México </t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2433,6 +3181,12 @@
       <c r="D125" t="n">
         <v>8844</v>
       </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Malasia </t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2449,6 +3203,12 @@
       <c r="D126" t="n">
         <v>710</v>
       </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mozambique </t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2465,6 +3225,12 @@
       <c r="D127" t="n">
         <v>2845</v>
       </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Namibia </t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2481,6 +3247,12 @@
       <c r="D128" t="n">
         <v>347</v>
       </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Níger </t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2497,6 +3269,12 @@
       <c r="D129" t="n">
         <v>435</v>
       </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nigeria </t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2513,6 +3291,12 @@
       <c r="D130" t="n">
         <v>1113</v>
       </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nicaragua </t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2529,6 +3313,12 @@
       <c r="D131" t="n">
         <v>29479</v>
       </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Países Bajos </t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2545,6 +3335,12 @@
       <c r="D132" t="n">
         <v>38399</v>
       </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Noruega </t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2561,6 +3357,12 @@
       <c r="D133" t="n">
         <v>700</v>
       </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nepal </t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2577,6 +3379,12 @@
       <c r="D134" t="n">
         <v>2380</v>
       </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nauru </t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2593,6 +3401,12 @@
       <c r="D135" t="n">
         <v>24539</v>
       </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nueva Zelanda </t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2609,6 +3423,12 @@
       <c r="D136" t="n">
         <v>7124</v>
       </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Omán </t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2625,6 +3445,12 @@
       <c r="D137" t="n">
         <v>11149</v>
       </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panamá </t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2641,6 +3467,12 @@
       <c r="D138" t="n">
         <v>2799</v>
       </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perú </t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2657,6 +3489,12 @@
       <c r="D139" t="n">
         <v>1495</v>
       </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Papúa Nueva Guinea </t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2673,6 +3511,12 @@
       <c r="D140" t="n">
         <v>2310</v>
       </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filipinas </t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2689,6 +3533,12 @@
       <c r="D141" t="n">
         <v>1108</v>
       </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pakistán </t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2705,6 +3555,12 @@
       <c r="D142" t="n">
         <v>13848</v>
       </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polonia </t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2721,6 +3577,12 @@
       <c r="D143" t="n">
         <v>1602</v>
       </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estado de Palestina </t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2737,6 +3599,12 @@
       <c r="D144" t="n">
         <v>11722</v>
       </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Palaos </t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2753,6 +3621,12 @@
       <c r="D145" t="n">
         <v>2890</v>
       </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paraguay </t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2769,6 +3643,12 @@
       <c r="D146" t="n">
         <v>30370</v>
       </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catar </t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2785,6 +3665,12 @@
       <c r="D147" t="n">
         <v>11552</v>
       </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rumanía </t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2801,6 +3687,12 @@
       <c r="D148" t="n">
         <v>6032</v>
       </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Serbia </t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2817,6 +3709,12 @@
       <c r="D149" t="n">
         <v>3012</v>
       </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rusia </t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2833,6 +3731,12 @@
       <c r="D150" t="n">
         <v>651</v>
       </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ruanda </t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2849,6 +3753,12 @@
       <c r="D151" t="n">
         <v>9185</v>
       </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arabia Saudita </t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2865,6 +3775,12 @@
       <c r="D152" t="n">
         <v>311</v>
       </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Islas Salomón </t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2881,6 +3797,12 @@
       <c r="D153" t="n">
         <v>12423</v>
       </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seychelles </t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2897,6 +3819,12 @@
       <c r="D154" t="n">
         <v>1386</v>
       </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sudán </t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2913,6 +3841,12 @@
       <c r="D155" t="n">
         <v>18810</v>
       </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suecia </t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2929,6 +3863,12 @@
       <c r="D156" t="n">
         <v>160490</v>
       </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Singapur </t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2945,6 +3885,12 @@
       <c r="D157" t="n">
         <v>22798</v>
       </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eslovenia </t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2961,6 +3907,12 @@
       <c r="D158" t="n">
         <v>14968</v>
       </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eslovaquia </t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2977,6 +3929,12 @@
       <c r="D159" t="n">
         <v>376</v>
       </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sierra Leona </t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2993,6 +3951,12 @@
       <c r="D160" t="n">
         <v>38250</v>
       </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Marino </t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3009,6 +3973,12 @@
       <c r="D161" t="n">
         <v>2259</v>
       </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senegal </t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3025,6 +3995,12 @@
       <c r="D162" t="n">
         <v>5313</v>
       </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surinam </t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3041,6 +4017,12 @@
       <c r="D163" t="n">
         <v>205</v>
       </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sudán del Sur </t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3057,6 +4039,12 @@
       <c r="D164" t="n">
         <v>2208</v>
       </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Santo Tomé y Príncipe </t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3073,6 +4061,12 @@
       <c r="D165" t="n">
         <v>4883</v>
       </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El Salvador </t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3089,6 +4083,12 @@
       <c r="D166" t="n">
         <v>798</v>
       </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Siria </t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3105,6 +4105,12 @@
       <c r="D167" t="n">
         <v>1498</v>
       </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eswatini </t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3121,6 +4127,12 @@
       <c r="D168" t="n">
         <v>335</v>
       </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chad </t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3137,6 +4149,12 @@
       <c r="D169" t="n">
         <v>738</v>
       </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Togo </t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3153,6 +4171,12 @@
       <c r="D170" t="n">
         <v>4557</v>
       </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tailandia </t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3169,6 +4193,12 @@
       <c r="D171" t="n">
         <v>352</v>
       </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tayikistán </t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3185,6 +4215,12 @@
       <c r="D172" t="n">
         <v>193</v>
       </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Timor Oriental </t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3201,6 +4237,12 @@
       <c r="D173" t="n">
         <v>428</v>
       </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turkmenistán </t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3217,6 +4259,12 @@
       <c r="D174" t="n">
         <v>3617</v>
       </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Túnez </t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3233,6 +4281,12 @@
       <c r="D175" t="n">
         <v>2152</v>
       </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tonga </t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3249,6 +4303,12 @@
       <c r="D176" t="n">
         <v>3811</v>
       </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Türkiye </t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3265,6 +4325,12 @@
       <c r="D177" t="n">
         <v>12035</v>
       </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinidad y Tobago </t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3281,6 +4347,12 @@
       <c r="D178" t="n">
         <v>391</v>
       </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tuvalu </t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3297,6 +4369,12 @@
       <c r="D179" t="n">
         <v>8973</v>
       </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taiwan </t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3313,6 +4391,12 @@
       <c r="D180" t="n">
         <v>562</v>
       </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tanzania </t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3329,6 +4413,12 @@
       <c r="D181" t="n">
         <v>4534</v>
       </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ucrania </t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3345,6 +4435,12 @@
       <c r="D182" t="n">
         <v>621</v>
       </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uganda </t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3361,6 +4457,12 @@
       <c r="D183" t="n">
         <v>15925</v>
       </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uruguay </t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3377,6 +4479,12 @@
       <c r="D184" t="n">
         <v>1017</v>
       </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uzbekistán </t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3393,6 +4501,12 @@
       <c r="D185" t="n">
         <v>10628</v>
       </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Vicente y las Granadinas </t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3409,6 +4523,12 @@
       <c r="D186" t="n">
         <v>985</v>
       </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venezuela </t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3425,6 +4545,12 @@
       <c r="D187" t="n">
         <v>1479</v>
       </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viet Nam </t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3441,6 +4567,12 @@
       <c r="D188" t="n">
         <v>1542</v>
       </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vanuatu </t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -3457,6 +4589,12 @@
       <c r="D189" t="n">
         <v>1415</v>
       </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samoa </t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -3473,6 +4611,12 @@
       <c r="D190" t="n">
         <v>344</v>
       </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yemen </t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3489,6 +4633,12 @@
       <c r="D191" t="n">
         <v>4849</v>
       </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sudáfrica </t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3505,6 +4655,12 @@
       <c r="D192" t="n">
         <v>1432</v>
       </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zambia </t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -3520,6 +4676,12 @@
       </c>
       <c r="D193" t="n">
         <v>36788</v>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zimbabue </t>
+        </is>
       </c>
     </row>
   </sheetData>
